--- a/assets/pdf/Project_Details.xlsx
+++ b/assets/pdf/Project_Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/midnight/Documents/local python/portfolio/assets/pdf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17F73A2-3A4C-E249-BDA5-F36925EA19F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE82D421-810B-AF4B-88DB-1AE1F981D6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="640" yWindow="780" windowWidth="30700" windowHeight="19580" xr2:uid="{CC705485-2A99-694A-9A0D-37A19C849311}"/>
   </bookViews>
@@ -205,9 +205,6 @@
     <t>#statistics, #hypothesis-testing, #python, #anomaly</t>
   </si>
   <si>
-    <t>#machine-learning, #time-series, #data-viz, #python, #anomaly</t>
-  </si>
-  <si>
     <t>A time-series forecasting and anomaly-detection tool that lets users upload any dataset, automatically identifies the date and value columns, and produces dual forecasts with Prophet and auto-tuned SARIMAX—complete with Isolation Forest anomaly overlays. Build using Streamlit.</t>
   </si>
   <si>
@@ -311,6 +308,9 @@
   </si>
   <si>
     <t>https://blog.dtucker.xyz/critical-path</t>
+  </si>
+  <si>
+    <t>#machine-learning, #time-series, #data-viz, #python, #anomaly, #streamlit</t>
   </si>
 </sst>
 </file>
@@ -741,13 +741,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -761,13 +761,13 @@
         <v>31</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="19" x14ac:dyDescent="0.2">
@@ -781,13 +781,13 @@
         <v>32</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -801,10 +801,10 @@
         <v>33</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -818,7 +818,7 @@
         <v>34</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -832,10 +832,10 @@
         <v>35</v>
       </c>
       <c r="D6" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="19" x14ac:dyDescent="0.2">
@@ -849,7 +849,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -863,10 +863,10 @@
         <v>36</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -880,13 +880,13 @@
         <v>37</v>
       </c>
       <c r="D9" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="19" x14ac:dyDescent="0.2">
@@ -900,10 +900,10 @@
         <v>38</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -917,10 +917,10 @@
         <v>44</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -934,10 +934,10 @@
         <v>39</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -951,10 +951,10 @@
         <v>40</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -968,10 +968,10 @@
         <v>41</v>
       </c>
       <c r="D14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="102" x14ac:dyDescent="0.2">
@@ -985,10 +985,10 @@
         <v>42</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="85" x14ac:dyDescent="0.2">
@@ -996,16 +996,16 @@
         <v>43</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">

--- a/assets/pdf/Project_Details.xlsx
+++ b/assets/pdf/Project_Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/midnight/Documents/local python/portfolio/assets/pdf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE82D421-810B-AF4B-88DB-1AE1F981D6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AEE96C-1CE5-F743-8A51-0E04EE9AE7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="640" yWindow="780" windowWidth="30700" windowHeight="19580" xr2:uid="{CC705485-2A99-694A-9A0D-37A19C849311}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="86">
   <si>
     <t>Project Description</t>
   </si>
@@ -311,6 +311,21 @@
   </si>
   <si>
     <t>#machine-learning, #time-series, #data-viz, #python, #anomaly, #streamlit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A3 Process Improvement App </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This A3 Process Improvement app is a React-based tool that guides users through Toyota's systematic problem-solving methodology using a focused, one-question-at-a-time interface. Built with Claude's help, it walks users through all eight A3 steps (from problem identification to follow-up planning), then uses Claude's API to automatically analyze their completed document and provide expert-level insights including key findings, recommendations, and risk assessments. </t>
+  </si>
+  <si>
+    <t>#process-improvement, #python, #A3, #claude, #LLM</t>
+  </si>
+  <si>
+    <t>https://claude.ai/public/artifacts/22829a62-eadf-439b-9aff-9c9c9a272106?fullscreen=false</t>
+  </si>
+  <si>
+    <t>https://blog.dtucker.xyz/building-an-a3-process-improvement-app-with-claude</t>
   </si>
 </sst>
 </file>
@@ -388,7 +403,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -404,6 +419,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1008,8 +1024,22 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B17" s="4"/>
+    <row r="17" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>85</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F16" xr:uid="{7A3B0A03-8EB4-CB41-AF88-81F423DD48CE}"/>
@@ -1045,6 +1075,8 @@
     <hyperlink ref="D15" r:id="rId29" xr:uid="{0FFF2171-5A6A-4A42-B01B-397559911F1E}"/>
     <hyperlink ref="F15" r:id="rId30" xr:uid="{9F2373FB-6C65-8D49-B848-30DCD85A6E5C}"/>
     <hyperlink ref="F13" r:id="rId31" xr:uid="{E9B14236-0847-C440-8591-02973605A162}"/>
+    <hyperlink ref="D17" r:id="rId32" xr:uid="{4BA1E85A-CA0B-D84B-B86F-707B9E1547EB}"/>
+    <hyperlink ref="F17" r:id="rId33" xr:uid="{0DCAD1BE-3BBA-6942-BB8D-9050FF7A61AD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/pdf/Project_Details.xlsx
+++ b/assets/pdf/Project_Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/midnight/Documents/local python/portfolio/assets/pdf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AEE96C-1CE5-F743-8A51-0E04EE9AE7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDF9AFB-6204-0D44-800F-6C8291F55582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="640" yWindow="780" windowWidth="30700" windowHeight="19580" xr2:uid="{CC705485-2A99-694A-9A0D-37A19C849311}"/>
   </bookViews>

--- a/assets/pdf/Project_Details.xlsx
+++ b/assets/pdf/Project_Details.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/midnight/Documents/local python/portfolio/assets/pdf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDF9AFB-6204-0D44-800F-6C8291F55582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD4330C-04E7-C64D-892D-080F17BD52EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="640" yWindow="780" windowWidth="30700" windowHeight="19580" xr2:uid="{CC705485-2A99-694A-9A0D-37A19C849311}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="89">
   <si>
     <t>Project Description</t>
   </si>
@@ -326,6 +326,15 @@
   </si>
   <si>
     <t>https://blog.dtucker.xyz/building-an-a3-process-improvement-app-with-claude</t>
+  </si>
+  <si>
+    <t>Software Development Process Improvement Integration</t>
+  </si>
+  <si>
+    <t>#process-improvement, #automation, #LLM</t>
+  </si>
+  <si>
+    <t>Worked on a cross-functional project to improve operational process flows through automation, standardization, and digital tool deployment. Served as a bridge between stakeholders and developers, helping translate business requirements into scalable solutions that applied deterministic and agentic logic to drive more consistent and efficient execution.</t>
   </si>
 </sst>
 </file>
@@ -735,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A3B0A03-8EB4-CB41-AF88-81F423DD48CE}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5" customWidth="1"/>
@@ -1039,6 +1048,17 @@
       </c>
       <c r="F17" s="6" t="s">
         <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/assets/pdf/Project_Details.xlsx
+++ b/assets/pdf/Project_Details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/midnight/Documents/local python/portfolio/assets/pdf/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dtuck/local python/portfolio/assets/pdf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD4330C-04E7-C64D-892D-080F17BD52EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E69C30A-8FFD-EA4D-A0F0-BE32B8DB8DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="640" yWindow="780" windowWidth="30700" windowHeight="19580" xr2:uid="{CC705485-2A99-694A-9A0D-37A19C849311}"/>
+    <workbookView xWindow="640" yWindow="600" windowWidth="30700" windowHeight="19500" xr2:uid="{CC705485-2A99-694A-9A0D-37A19C849311}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="92">
   <si>
     <t>Project Description</t>
   </si>
@@ -335,6 +335,15 @@
   </si>
   <si>
     <t>Worked on a cross-functional project to improve operational process flows through automation, standardization, and digital tool deployment. Served as a bridge between stakeholders and developers, helping translate business requirements into scalable solutions that applied deterministic and agentic logic to drive more consistent and efficient execution.</t>
+  </si>
+  <si>
+    <t>Parsing freeform text</t>
+  </si>
+  <si>
+    <t>#LLM, #python</t>
+  </si>
+  <si>
+    <t>Python script that uses an LLM to parse free form transportation move data from Excel files in batches, extracting location and object moved.</t>
   </si>
 </sst>
 </file>
@@ -744,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A3B0A03-8EB4-CB41-AF88-81F423DD48CE}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5" customWidth="1"/>
@@ -1059,6 +1068,17 @@
       </c>
       <c r="C18" s="4" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
